--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.91640154592377</v>
+        <v>2.748915251212613</v>
       </c>
       <c r="D2" t="n">
-        <v>17.39533580063208</v>
+        <v>2.826742067602712</v>
       </c>
       <c r="E2" t="n">
-        <v>6.855820732305341</v>
+        <v>1.114070868999618</v>
       </c>
       <c r="F2" t="n">
-        <v>6.672653046204097</v>
+        <v>1.084306120008166</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.6883855022102</v>
+        <v>2.874362644109158</v>
       </c>
       <c r="D3" t="n">
-        <v>16.79340449750658</v>
+        <v>2.728928230844819</v>
       </c>
       <c r="E3" t="n">
-        <v>6.855820732305341</v>
+        <v>1.114070868999618</v>
       </c>
       <c r="F3" t="n">
-        <v>6.672653046204097</v>
+        <v>1.084306120008166</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2.774376412664203</v>
+        <v>0.4508361670579329</v>
       </c>
       <c r="D4" t="n">
-        <v>2.949137628275831</v>
+        <v>0.4792348645948226</v>
       </c>
       <c r="E4" t="n">
-        <v>6.855820732305341</v>
+        <v>1.114070868999618</v>
       </c>
       <c r="F4" t="n">
-        <v>6.672653046204097</v>
+        <v>1.084306120008166</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
